--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487728_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487728_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.3439</v>
+        <v>7.0801</v>
       </c>
       <c r="E2" t="n">
-        <v>7.8121</v>
+        <v>7.7936</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.4682</v>
+        <v>-0.7135</v>
       </c>
       <c r="G2" t="n">
         <v>7.6978</v>
@@ -610,13 +610,13 @@
         <v>1.5523</v>
       </c>
       <c r="S2" t="n">
-        <v>1.9462</v>
+        <v>1.6824</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5596</v>
+        <v>0.5411</v>
       </c>
       <c r="U2" t="n">
-        <v>1.3865</v>
+        <v>1.1412</v>
       </c>
       <c r="V2" t="n">
         <v>-0.9418</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.9693</v>
+        <v>5.402</v>
       </c>
       <c r="E3" t="n">
-        <v>4.8481</v>
+        <v>4.3081</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1212</v>
+        <v>1.0939</v>
       </c>
       <c r="G3" t="n">
         <v>2.4802</v>
@@ -688,13 +688,13 @@
         <v>1.5523</v>
       </c>
       <c r="S3" t="n">
-        <v>1.607</v>
+        <v>1.0397</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5473</v>
+        <v>0.0073</v>
       </c>
       <c r="U3" t="n">
-        <v>1.0597</v>
+        <v>1.0324</v>
       </c>
       <c r="V3" t="n">
         <v>0.3299</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.3172</v>
+        <v>3.8392</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5322</v>
+        <v>2.354</v>
       </c>
       <c r="F4" t="n">
-        <v>1.785</v>
+        <v>1.4852</v>
       </c>
       <c r="G4" t="n">
         <v>2.4277</v>
@@ -766,13 +766,13 @@
         <v>0.7761</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8298</v>
+        <v>1.3518</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6539</v>
+        <v>0.1679</v>
       </c>
       <c r="U4" t="n">
-        <v>1.4837</v>
+        <v>1.1838</v>
       </c>
       <c r="V4" t="n">
         <v>1.2239</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4583</v>
+        <v>2.728</v>
       </c>
       <c r="E5" t="n">
-        <v>2.5448</v>
+        <v>2.7055</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0866</v>
+        <v>0.0225</v>
       </c>
       <c r="G5" t="n">
         <v>0.9067</v>
@@ -844,13 +844,13 @@
         <v>0.3881</v>
       </c>
       <c r="S5" t="n">
-        <v>1.1157</v>
+        <v>1.3854</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4374</v>
+        <v>0.5981</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6783</v>
+        <v>0.7874</v>
       </c>
       <c r="V5" t="n">
         <v>0.0478</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5655</v>
+        <v>2.6049</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.734</v>
+        <v>-0.2125</v>
       </c>
       <c r="F6" t="n">
-        <v>2.2995</v>
+        <v>2.8173</v>
       </c>
       <c r="G6" t="n">
         <v>0.1714</v>
@@ -922,13 +922,13 @@
         <v>1.5523</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8179</v>
+        <v>0.2215</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.0296</v>
+        <v>-0.5081</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2118</v>
+        <v>0.7296</v>
       </c>
       <c r="V6" t="n">
         <v>0.6597</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. GARCIA QUILEZ CUERVAS</t>
+          <t>G. MARTIN LOPEZ-LAGO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.166</v>
+        <v>0.3556</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.0236</v>
+        <v>-1.6535</v>
       </c>
       <c r="F7" t="n">
-        <v>1.1896</v>
+        <v>2.0091</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.1959</v>
+        <v>1.2943</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.9491000000000001</v>
+        <v>-1.1938</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.2468</v>
+        <v>2.4881</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.1322</v>
+        <v>2.8045</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.7085</v>
+        <v>0.1607</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.4237</v>
+        <v>2.6438</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.0637</v>
+        <v>-1.5102</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2406</v>
+        <v>-1.3545</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.8231000000000001</v>
+        <v>-0.1557</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.9702</v>
+        <v>-2.9105</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9403</v>
+        <v>-4.8508</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9702</v>
+        <v>1.9403</v>
       </c>
       <c r="S7" t="n">
-        <v>3.0022</v>
+        <v>1.2643</v>
       </c>
       <c r="T7" t="n">
-        <v>2.3788</v>
+        <v>0.3928</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6234</v>
+        <v>0.8715000000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3299</v>
+        <v>0.7075</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.3299</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6597</v>
+        <v>0.7075</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1163</v>
+        <v>0.07770000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.21</v>
+        <v>-0.9887</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0937</v>
+        <v>1.0664</v>
       </c>
       <c r="G8" t="n">
         <v>-0.09810000000000001</v>
@@ -1078,13 +1078,13 @@
         <v>1.7463</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1759</v>
+        <v>0.3698</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1806</v>
+        <v>0.0406</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3565</v>
+        <v>0.3292</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4405</v>
+        <v>-0.6858</v>
       </c>
       <c r="E9" t="n">
         <v>-0.9091</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4687</v>
+        <v>0.2234</v>
       </c>
       <c r="G9" t="n">
         <v>-0.8651</v>
@@ -1156,13 +1156,13 @@
         <v>1.3582</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6485</v>
+        <v>0.4032</v>
       </c>
       <c r="T9" t="n">
         <v>0.0011</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6474</v>
+        <v>0.4021</v>
       </c>
       <c r="V9" t="n">
         <v>-0.6119</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G. MARTIN LOPEZ-LAGO</t>
+          <t>A. GARCIA QUILEZ CUERVAS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.5446</v>
+        <v>-0.9018</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.3357</v>
+        <v>-2.0641</v>
       </c>
       <c r="F10" t="n">
-        <v>1.791</v>
+        <v>1.1623</v>
       </c>
       <c r="G10" t="n">
-        <v>1.2943</v>
+        <v>-2.1959</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.1938</v>
+        <v>-0.9491000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>2.4881</v>
+        <v>-1.2468</v>
       </c>
       <c r="J10" t="n">
-        <v>2.8045</v>
+        <v>-1.1322</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1607</v>
+        <v>-0.7085</v>
       </c>
       <c r="L10" t="n">
-        <v>2.6438</v>
+        <v>-0.4237</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.5102</v>
+        <v>-1.0637</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.3545</v>
+        <v>-0.2406</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1557</v>
+        <v>-0.8231000000000001</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.9105</v>
+        <v>-0.9702</v>
       </c>
       <c r="Q10" t="n">
-        <v>-4.8508</v>
+        <v>-1.9403</v>
       </c>
       <c r="R10" t="n">
-        <v>1.9403</v>
+        <v>0.9702</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3641</v>
+        <v>1.9344</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2894</v>
+        <v>1.3383</v>
       </c>
       <c r="U10" t="n">
-        <v>0.6535</v>
+        <v>0.5961</v>
       </c>
       <c r="V10" t="n">
-        <v>0.7075</v>
+        <v>0.3299</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-0.3299</v>
       </c>
       <c r="X10" t="n">
-        <v>0.7075</v>
+        <v>0.6597</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.1103</v>
+        <v>-0.9829</v>
       </c>
       <c r="E11" t="n">
-        <v>2.0327</v>
+        <v>2.1328</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.143</v>
+        <v>-3.1157</v>
       </c>
       <c r="G11" t="n">
         <v>-0.8871</v>
@@ -1312,13 +1312,13 @@
         <v>0.7761</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2245</v>
+        <v>0.3519</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3039</v>
+        <v>0.404</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0794</v>
+        <v>-0.0521</v>
       </c>
       <c r="V11" t="n">
         <v>-1.2239</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>18.6085</v>
+        <v>19.517</v>
       </c>
       <c r="E12" t="n">
-        <v>12.5575</v>
+        <v>13.4661</v>
       </c>
       <c r="F12" t="n">
-        <v>6.0509</v>
+        <v>6.050899999999999</v>
       </c>
       <c r="G12" t="n">
         <v>10.9319</v>
@@ -1369,19 +1369,19 @@
         <v>11.6745</v>
       </c>
       <c r="L12" t="n">
-        <v>7.619300000000001</v>
+        <v>7.619299999999999</v>
       </c>
       <c r="M12" t="n">
         <v>-8.361700000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>-8.222399999999999</v>
+        <v>-8.2224</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.1391999999999999</v>
+        <v>-0.1392000000000001</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.9402</v>
+        <v>-1.940199999999999</v>
       </c>
       <c r="Q12" t="n">
         <v>-14.5524</v>
@@ -1390,16 +1390,16 @@
         <v>12.6122</v>
       </c>
       <c r="S12" t="n">
-        <v>9.096000000000002</v>
+        <v>10.0044</v>
       </c>
       <c r="T12" t="n">
-        <v>2.0746</v>
+        <v>2.9831</v>
       </c>
       <c r="U12" t="n">
-        <v>7.021400000000001</v>
+        <v>7.021199999999999</v>
       </c>
       <c r="V12" t="n">
-        <v>0.5211000000000001</v>
+        <v>0.5211000000000003</v>
       </c>
       <c r="W12" t="n">
         <v>5.7417</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.1133</v>
+        <v>5.2378</v>
       </c>
       <c r="E13" t="n">
-        <v>6.1824</v>
+        <v>6.2825</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.0691</v>
+        <v>-1.0447</v>
       </c>
       <c r="G13" t="n">
         <v>1.9385</v>
@@ -1468,13 +1468,13 @@
         <v>1.7463</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.0193</v>
+        <v>-0.8947000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8479</v>
+        <v>-0.7478</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1713</v>
+        <v>-0.1469</v>
       </c>
       <c r="V13" t="n">
         <v>2.4477</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1064</v>
+        <v>0.152</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0873</v>
+        <v>0.1874</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0191</v>
+        <v>-0.0354</v>
       </c>
       <c r="G14" t="n">
         <v>0.6208</v>
@@ -1546,13 +1546,13 @@
         <v>0.5821</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.4367</v>
+        <v>-0.3911</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3028</v>
+        <v>-0.2027</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1339</v>
+        <v>-0.1884</v>
       </c>
       <c r="V14" t="n">
         <v>-0.6597</v>
@@ -1579,10 +1579,10 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.4419</v>
+        <v>-0.8423</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.2299</v>
+        <v>-0.6303</v>
       </c>
       <c r="F15" t="n">
         <v>-0.2119</v>
@@ -1624,10 +1624,10 @@
         <v>0.194</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4733</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>0.7402</v>
+        <v>0.3398</v>
       </c>
       <c r="U15" t="n">
         <v>-0.2669</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.2731</v>
+        <v>-1.0667</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8</v>
+        <v>0.9001</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.073</v>
+        <v>-1.9668</v>
       </c>
       <c r="G16" t="n">
         <v>2.534</v>
@@ -1702,13 +1702,13 @@
         <v>2.1344</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.4011</v>
+        <v>-1.1948</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.5747</v>
+        <v>-1.4746</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1737</v>
+        <v>0.2799</v>
       </c>
       <c r="V16" t="n">
         <v>-0.6597</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.9454</v>
+        <v>-1.4665</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.7063</v>
+        <v>-0.6062</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.2391</v>
+        <v>-0.8603</v>
       </c>
       <c r="G17" t="n">
         <v>-1.5093</v>
@@ -1780,13 +1780,13 @@
         <v>1.5523</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.3764</v>
+        <v>-0.8975</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6057</v>
+        <v>-0.5056</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.7707000000000001</v>
+        <v>-0.392</v>
       </c>
       <c r="V17" t="n">
         <v>-0.6119</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.1213</v>
+        <v>-2.3972</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.4426</v>
+        <v>-1.7429</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.6787</v>
+        <v>-0.6543</v>
       </c>
       <c r="G18" t="n">
         <v>-1.1973</v>
@@ -1858,13 +1858,13 @@
         <v>1.7463</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4002</v>
+        <v>-0.676</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2894</v>
+        <v>-0.5897</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1108</v>
+        <v>-0.0863</v>
       </c>
       <c r="V18" t="n">
         <v>-0.3299</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.5885</v>
+        <v>-3.2159</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.1737</v>
+        <v>-2.474</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.4148</v>
+        <v>-0.7419</v>
       </c>
       <c r="G19" t="n">
         <v>-4.4812</v>
@@ -1936,13 +1936,13 @@
         <v>1.3582</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.255</v>
+        <v>-0.8824</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5317</v>
+        <v>-0.832</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2766</v>
+        <v>-0.0504</v>
       </c>
       <c r="V19" t="n">
         <v>2.7298</v>
@@ -1969,10 +1969,10 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.53</v>
+        <v>-3.3298</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.5698</v>
+        <v>-1.3696</v>
       </c>
       <c r="F20" t="n">
         <v>-1.9602</v>
@@ -2014,10 +2014,10 @@
         <v>1.1642</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.0307</v>
+        <v>-0.8305</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9567</v>
+        <v>-0.7565</v>
       </c>
       <c r="U20" t="n">
         <v>-0.074</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.7456</v>
+        <v>-3.4548</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.8818</v>
+        <v>-2.7817</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8639</v>
+        <v>-0.6731</v>
       </c>
       <c r="G21" t="n">
         <v>-3.1644</v>
@@ -2092,13 +2092,13 @@
         <v>1.3582</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.3275</v>
+        <v>-1.0366</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7874</v>
+        <v>-0.6873</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5401</v>
+        <v>-0.3494</v>
       </c>
       <c r="V21" t="n">
         <v>-0.6119</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.0078</v>
+        <v>-3.747</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.79</v>
+        <v>-1.6899</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.2178</v>
+        <v>-2.0571</v>
       </c>
       <c r="G22" t="n">
         <v>-0.4774</v>
@@ -2170,13 +2170,13 @@
         <v>1.3582</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7826</v>
+        <v>-0.5218</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6662</v>
+        <v>-0.5661</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1164</v>
+        <v>0.0443</v>
       </c>
       <c r="V22" t="n">
         <v>-2.1657</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.1746</v>
+        <v>-3.8108</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.3265</v>
+        <v>-2.1263</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.8481</v>
+        <v>-1.6845</v>
       </c>
       <c r="G23" t="n">
         <v>-3.5871</v>
@@ -2248,13 +2248,13 @@
         <v>1.3582</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.5397</v>
+        <v>-1.176</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.199</v>
+        <v>-0.9988</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3407</v>
+        <v>-0.1772</v>
       </c>
       <c r="V23" t="n">
         <v>0.5642</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-18.6085</v>
+        <v>-17.9412</v>
       </c>
       <c r="E24" t="n">
         <v>-6.0509</v>
       </c>
       <c r="F24" t="n">
-        <v>-12.5575</v>
+        <v>-11.8902</v>
       </c>
       <c r="G24" t="n">
         <v>-10.9319</v>
@@ -2326,13 +2326,13 @@
         <v>14.5524</v>
       </c>
       <c r="S24" t="n">
-        <v>-9.095899999999999</v>
+        <v>-8.4285</v>
       </c>
       <c r="T24" t="n">
-        <v>-7.021299999999999</v>
+        <v>-7.021300000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>-2.0745</v>
+        <v>-1.4073</v>
       </c>
       <c r="V24" t="n">
         <v>-0.5209999999999999</v>
